--- a/data/raw/2026/1-6月/旅游.xlsx
+++ b/data/raw/2026/1-6月/旅游.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ39"/>
+  <dimension ref="A1:BZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4952,7 +4952,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>旅行社工作人员</t>
+          <t>游客</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>浙江省外</t>
+          <t>浙江省内</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>华北地区（京、津、冀、晋、蒙）</t>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -5147,14 +5147,14 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
           <t>会推荐</t>
@@ -5162,27 +5162,27 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>2026-06-15 10:26:02</t>
+          <t>2026-06-27 17:21:22</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>2026-06-15 10:26:02</t>
+          <t>2026-06-27 17:21:22</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/688849487a7c4563aa8fc3aa9919a60f.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c8ba7508fb8141bd890e91308a9f4b17.mp3</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 分 7 秒 </t>
+          <t xml:space="preserve">1 分 20 秒 </t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>2026-06-15 10:21:52</t>
+          <t>2026-06-27 17:20:00</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -5234,7 +5234,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5259,32 +5259,37 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t>华南地区（粤、桂、琼、港、澳、台）</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -5299,12 +5304,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -5319,7 +5324,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -5399,12 +5404,12 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5424,47 +5429,47 @@
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>会推荐</t>
+          <t>可能会推荐</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>2026-06-12 15:06:14</t>
+          <t>2026-06-27 17:19:17</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>2026-06-12 15:06:14</t>
+          <t>2026-06-27 17:19:17</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4b6b1707600b4d6da18f39e4e02b0aec.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/6e8945e2750b44fd953c4f1a7fcfdcf9.mp3</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 34 秒 </t>
+          <t xml:space="preserve">1 分 51 秒 </t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>2026-06-12 15:04:37</t>
+          <t>2026-06-27 17:17:23</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -5489,7 +5494,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -5516,7 +5521,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>125</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5554,7 +5559,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5706,7 +5711,7 @@
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -5726,27 +5731,27 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>2026-06-12 15:04:13</t>
+          <t>2026-06-27 17:16:35</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>2026-06-12 15:04:13</t>
+          <t>2026-06-27 17:16:35</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ac25982e2a7d49e8b52d0d034d9f5291.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/abeaa037cb934229826e56fa2e3a22b8.mp3</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 20 秒 </t>
+          <t xml:space="preserve">1 分 32 秒 </t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>2026-06-12 15:02:51</t>
+          <t>2026-06-27 17:15:00</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -5771,7 +5776,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -5798,7 +5803,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5823,20 +5828,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>西南地区（渝、川、贵、云、藏）</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5988,47 +5993,47 @@
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>趣味性</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>会推荐</t>
+          <t>可能会推荐</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:51:36</t>
+          <t>2026-06-27 17:14:13</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:51:36</t>
+          <t>2026-06-27 17:14:13</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/60378736b519470fa0370760081b0179.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/9d5a8d615b5244c6a5d0084ee55b8067.mp3</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 35 秒 </t>
+          <t xml:space="preserve">1 分 46 秒 </t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:49:59</t>
+          <t>2026-06-27 17:12:24</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -6053,7 +6058,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -6080,7 +6085,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6118,7 +6123,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6270,7 +6275,7 @@
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>专业知识</t>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -6290,27 +6295,27 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:48:39</t>
+          <t>2026-06-27 17:12:06</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:48:39</t>
+          <t>2026-06-27 17:12:06</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7aab0221f58f44e489a3d8437eb79f0f.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ac33a712f2fd4fed99720d955322f990.mp3</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 11 秒 </t>
+          <t xml:space="preserve">2 分 6 秒 </t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:46:25</t>
+          <t>2026-06-27 17:09:57</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -6335,7 +6340,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -6362,7 +6367,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6382,12 +6387,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6400,7 +6405,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6427,12 +6432,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -6447,12 +6452,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -6467,7 +6472,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -6542,29 +6547,19 @@
       </c>
       <c r="BC22" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>人工讲解导览</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>专业知识</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
           <t>会推荐</t>
@@ -6572,27 +6567,27 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:42:02</t>
+          <t>2026-06-27 17:09:38</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:42:02</t>
+          <t>2026-06-27 17:09:38</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b613c77d706547159084e32c857eb61a.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/426fc307dc5d47128bd49d3c106866a8.mp3</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 15 秒 </t>
+          <t xml:space="preserve">1 分 51 秒 </t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:39:44</t>
+          <t>2026-06-27 17:07:43</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -6617,7 +6612,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -6644,7 +6639,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6654,7 +6649,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>旅行社工作人员</t>
+          <t>游客</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6664,7 +6659,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6674,12 +6669,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>华中地区（豫、鄂、湘）</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -6687,6 +6682,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>10</t>
@@ -6824,7 +6824,17 @@
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -6844,27 +6854,27 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>2026-06-11 13:58:15</t>
+          <t>2026-06-27 17:03:48</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>2026-06-11 13:58:15</t>
+          <t>2026-06-27 17:03:48</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/6fa8f1c92ca142e7be7ffbbb3d81f458.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/18be09daad30445f87e6d2dda194aae3.mp3</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 20 秒 </t>
+          <t xml:space="preserve">1 分 43 秒 </t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>2026-06-11 13:55:51</t>
+          <t>2026-06-27 17:02:02</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -6889,7 +6899,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -6916,7 +6926,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6941,7 +6951,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7081,12 +7091,12 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7111,14 +7121,14 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG24" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
           <t>会推荐</t>
@@ -7126,27 +7136,27 @@
       </c>
       <c r="BM24" t="inlineStr">
         <is>
-          <t>2026-06-10 16:31:20</t>
+          <t>2026-06-27 17:01:48</t>
         </is>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>2026-06-10 16:31:20</t>
+          <t>2026-06-27 17:01:48</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c708bb5d4fc2411d84b19bce38caf78e.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/915ebff326dd4ce3adebfac252aa297c.mp3</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 43 秒 </t>
+          <t xml:space="preserve">1 分 37 秒 </t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>2026-06-10 16:29:34</t>
+          <t>2026-06-27 17:00:08</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -7171,7 +7181,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -7198,7 +7208,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7218,22 +7228,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>华南地区（粤、桂、琼、港、澳、台）</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7241,6 +7251,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>10</t>
@@ -7388,7 +7403,7 @@
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>故事性</t>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
@@ -7408,27 +7423,27 @@
       </c>
       <c r="BM25" t="inlineStr">
         <is>
-          <t>2026-06-10 16:25:08</t>
+          <t>2026-06-27 16:59:12</t>
         </is>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>2026-06-10 16:25:08</t>
+          <t>2026-06-27 16:59:12</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/67439ceb4fa84c81b9c5158dc36c3977.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/f3959074cb35474bb732d233260d9403.mp3</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 43 秒 </t>
+          <t xml:space="preserve">2 分 36 秒 </t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>2026-06-10 16:23:22</t>
+          <t>2026-06-27 16:56:32</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -7453,7 +7468,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -7480,7 +7495,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7490,22 +7505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅行社工作人员</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>2次及以上</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7690,27 +7705,27 @@
       </c>
       <c r="BM26" t="inlineStr">
         <is>
-          <t>2026-06-10 16:18:03</t>
+          <t>2026-06-27 16:55:38</t>
         </is>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>2026-06-10 16:18:03</t>
+          <t>2026-06-27 16:55:38</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b6e8b103655e411f99f680cd540373c7.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/98bb874799794a0a96f6f36feb8298a9.mp3</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 53 秒 </t>
+          <t xml:space="preserve">1 分 57 秒 </t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>2026-06-10 16:16:07</t>
+          <t>2026-06-27 16:53:38</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -7735,7 +7750,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -7762,7 +7777,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7772,7 +7787,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅行社工作人员</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7782,22 +7797,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>浙江省内</t>
+          <t>浙江省外</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+          <t>华北地区（京、津、冀、晋、蒙）</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -7817,12 +7832,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -7952,12 +7967,12 @@
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>故事性</t>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
@@ -7972,27 +7987,27 @@
       </c>
       <c r="BM27" t="inlineStr">
         <is>
-          <t>2026-06-10 15:40:01</t>
+          <t>2026-06-15 10:26:02</t>
         </is>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>2026-06-10 15:40:01</t>
+          <t>2026-06-15 10:26:02</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4e8e113158964b958db9709388aa6a1d.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/688849487a7c4563aa8fc3aa9919a60f.mp3</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 52 秒 </t>
+          <t xml:space="preserve">4 分 7 秒 </t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>2026-06-10 15:38:06</t>
+          <t>2026-06-15 10:21:52</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -8017,7 +8032,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -8044,7 +8059,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8064,7 +8079,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8082,7 +8097,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8239,7 +8254,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
@@ -8254,27 +8269,27 @@
       </c>
       <c r="BM28" t="inlineStr">
         <is>
-          <t>2026-06-10 15:36:01</t>
+          <t>2026-06-12 15:06:14</t>
         </is>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>2026-06-10 15:36:01</t>
+          <t>2026-06-12 15:06:14</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/867f99d38a12471cb62d79ed221cab5c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4b6b1707600b4d6da18f39e4e02b0aec.mp3</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 10 秒 </t>
+          <t xml:space="preserve">1 分 34 秒 </t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>2026-06-10 15:33:47</t>
+          <t>2026-06-12 15:04:37</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -8299,7 +8314,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -8326,7 +8341,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8346,12 +8361,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8364,7 +8379,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8536,27 +8551,27 @@
       </c>
       <c r="BM29" t="inlineStr">
         <is>
-          <t>2026-06-10 15:29:55</t>
+          <t>2026-06-12 15:04:13</t>
         </is>
       </c>
       <c r="BN29" t="inlineStr">
         <is>
-          <t>2026-06-10 15:29:55</t>
+          <t>2026-06-12 15:04:13</t>
         </is>
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ce654b0e29e243c2a973d4f2da16328c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ac25982e2a7d49e8b52d0d034d9f5291.mp3</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 2 秒 </t>
+          <t xml:space="preserve">1 分 20 秒 </t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>2026-06-10 15:27:50</t>
+          <t>2026-06-12 15:02:51</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -8581,7 +8596,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -8608,7 +8623,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8618,7 +8633,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>旅行社工作人员</t>
+          <t>游客</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -8628,12 +8643,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8646,7 +8661,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8818,27 +8833,27 @@
       </c>
       <c r="BM30" t="inlineStr">
         <is>
-          <t>2026-06-10 15:21:56</t>
+          <t>2026-06-12 14:51:36</t>
         </is>
       </c>
       <c r="BN30" t="inlineStr">
         <is>
-          <t>2026-06-10 15:21:56</t>
+          <t>2026-06-12 14:51:36</t>
         </is>
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/621680565b774e0680af6c501e9b88f5.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/60378736b519470fa0370760081b0179.mp3</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 51 秒 </t>
+          <t xml:space="preserve">1 分 35 秒 </t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>2026-06-10 15:20:02</t>
+          <t>2026-06-12 14:49:59</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -8863,7 +8878,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -8890,7 +8905,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8915,7 +8930,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8928,14 +8943,14 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -8955,7 +8970,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -9055,12 +9070,12 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9080,7 +9095,7 @@
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>故事性</t>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
@@ -9100,27 +9115,27 @@
       </c>
       <c r="BM31" t="inlineStr">
         <is>
-          <t>2026-06-10 15:17:56</t>
+          <t>2026-06-12 14:48:39</t>
         </is>
       </c>
       <c r="BN31" t="inlineStr">
         <is>
-          <t>2026-06-10 15:17:56</t>
+          <t>2026-06-12 14:48:39</t>
         </is>
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/e4660a6e7b1b4fc7ae2a637e5cfa8292.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7aab0221f58f44e489a3d8437eb79f0f.mp3</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 </t>
+          <t xml:space="preserve">2 分 11 秒 </t>
         </is>
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>2026-06-10 15:15:53</t>
+          <t>2026-06-12 14:46:25</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -9145,7 +9160,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -9172,7 +9187,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9192,25 +9207,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>浙江省外</t>
+          <t>浙江省内</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>西南地区（渝、川、贵、云、藏）</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9382,27 +9397,27 @@
       </c>
       <c r="BM32" t="inlineStr">
         <is>
-          <t>2026-06-10 15:10:53</t>
+          <t>2026-06-12 14:42:02</t>
         </is>
       </c>
       <c r="BN32" t="inlineStr">
         <is>
-          <t>2026-06-10 15:10:53</t>
+          <t>2026-06-12 14:42:02</t>
         </is>
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/bda17dbf386f421389ed6370f811d70d.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b613c77d706547159084e32c857eb61a.mp3</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 4 秒 </t>
+          <t xml:space="preserve">2 分 15 秒 </t>
         </is>
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>2026-06-10 15:07:46</t>
+          <t>2026-06-12 14:39:44</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -9427,7 +9442,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -9454,7 +9469,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9464,7 +9479,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>游客</t>
+          <t>旅行社工作人员</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9634,29 +9649,19 @@
       </c>
       <c r="BC33" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BD33" t="inlineStr">
-        <is>
-          <t>人工讲解导览</t>
-        </is>
-      </c>
-      <c r="BE33" t="inlineStr">
-        <is>
-          <t>专业知识</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
+      <c r="BG33" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
           <t>会推荐</t>
@@ -9664,27 +9669,27 @@
       </c>
       <c r="BM33" t="inlineStr">
         <is>
-          <t>2026-06-10 15:00:43</t>
+          <t>2026-06-11 13:58:15</t>
         </is>
       </c>
       <c r="BN33" t="inlineStr">
         <is>
-          <t>2026-06-10 15:00:43</t>
+          <t>2026-06-11 13:58:15</t>
         </is>
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/86b9a3463f6b40988e95832b993002f4.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/6fa8f1c92ca142e7be7ffbbb3d81f458.mp3</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 26 秒 </t>
+          <t xml:space="preserve">2 分 20 秒 </t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>2026-06-10 14:58:14</t>
+          <t>2026-06-11 13:55:51</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -9709,7 +9714,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -9736,7 +9741,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9756,7 +9761,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9901,12 +9906,12 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -9946,27 +9951,27 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>2026-06-10 14:57:25</t>
+          <t>2026-06-10 16:31:20</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>2026-06-10 14:57:25</t>
+          <t>2026-06-10 16:31:20</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a20165306c164ddfa57672b5816d8b5c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c708bb5d4fc2411d84b19bce38caf78e.mp3</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 12 秒 </t>
+          <t xml:space="preserve">1 分 43 秒 </t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>2026-06-10 14:55:09</t>
+          <t>2026-06-10 16:29:34</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -9991,7 +9996,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -10018,7 +10023,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10033,7 +10038,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2次及以上</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10043,7 +10048,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -10056,7 +10061,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10093,12 +10098,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -10153,12 +10158,12 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -10198,7 +10203,17 @@
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>故事性</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -10218,27 +10233,27 @@
       </c>
       <c r="BM35" t="inlineStr">
         <is>
-          <t>2026-06-05 16:40:49</t>
+          <t>2026-06-10 16:25:08</t>
         </is>
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>2026-06-05 16:40:49</t>
+          <t>2026-06-10 16:25:08</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/53b5194f2d7c4bc0ba8dd14e9afe4caa.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/67439ceb4fa84c81b9c5158dc36c3977.mp3</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 49 秒 </t>
+          <t xml:space="preserve">1 分 43 秒 </t>
         </is>
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>2026-06-05 16:38:57</t>
+          <t>2026-06-10 16:23:22</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
@@ -10263,7 +10278,7 @@
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW35" t="inlineStr">
@@ -10290,7 +10305,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10310,12 +10325,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10328,7 +10343,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10365,12 +10380,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -10425,12 +10440,12 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -10470,7 +10485,17 @@
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>专业知识</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -10490,27 +10515,27 @@
       </c>
       <c r="BM36" t="inlineStr">
         <is>
-          <t>2026-06-05 14:36:31</t>
+          <t>2026-06-10 16:18:03</t>
         </is>
       </c>
       <c r="BN36" t="inlineStr">
         <is>
-          <t>2026-06-05 14:36:31</t>
+          <t>2026-06-10 16:18:03</t>
         </is>
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/d5ec9c3050de4f11b78de3480848d88f.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b6e8b103655e411f99f680cd540373c7.mp3</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 23 秒 </t>
+          <t xml:space="preserve">1 分 53 秒 </t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>2026-06-05 14:35:05</t>
+          <t>2026-06-10 16:16:07</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
@@ -10535,7 +10560,7 @@
       </c>
       <c r="BV36" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体中心国博壁球馆</t>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW36" t="inlineStr">
@@ -10562,7 +10587,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10577,7 +10602,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2次及以上</t>
+          <t>首次</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10587,7 +10612,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -10600,14 +10625,14 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -10627,7 +10652,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -10637,12 +10662,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -10697,12 +10722,12 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -10727,12 +10752,12 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -10742,19 +10767,29 @@
       </c>
       <c r="BC37" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>故事性</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BF37" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
           <t>会推荐</t>
@@ -10762,27 +10797,27 @@
       </c>
       <c r="BM37" t="inlineStr">
         <is>
-          <t>2026-06-05 14:33:55</t>
+          <t>2026-06-10 15:40:01</t>
         </is>
       </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>2026-06-05 14:33:55</t>
+          <t>2026-06-10 15:40:01</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/384cba67e55b4a6ba45ed7d200dd5945.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/4e8e113158964b958db9709388aa6a1d.mp3</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 38 秒 </t>
+          <t xml:space="preserve">1 分 52 秒 </t>
         </is>
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>2026-06-05 14:32:15</t>
+          <t>2026-06-10 15:38:06</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
@@ -10807,7 +10842,7 @@
       </c>
       <c r="BV37" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW37" t="inlineStr">
@@ -10834,7 +10869,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10859,7 +10894,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -10872,7 +10907,7 @@
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10909,12 +10944,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -11014,14 +11049,24 @@
       </c>
       <c r="BC38" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="BG38" t="inlineStr">
         <is>
           <t>是</t>
@@ -11034,27 +11079,27 @@
       </c>
       <c r="BM38" t="inlineStr">
         <is>
-          <t>2026-06-05 12:30:06</t>
+          <t>2026-06-10 15:36:01</t>
         </is>
       </c>
       <c r="BN38" t="inlineStr">
         <is>
-          <t>2026-06-05 12:30:06</t>
+          <t>2026-06-10 15:36:01</t>
         </is>
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b5f5c6a9b4f14082913aafc79904c9cd.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/867f99d38a12471cb62d79ed221cab5c.mp3</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 51 秒 </t>
+          <t xml:space="preserve">2 分 10 秒 </t>
         </is>
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>2026-06-05 12:28:12</t>
+          <t>2026-06-10 15:33:47</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
@@ -11079,7 +11124,7 @@
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BW38" t="inlineStr">
@@ -11106,275 +11151,3055 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM39" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:29:55</t>
+        </is>
+      </c>
+      <c r="BN39" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:29:55</t>
+        </is>
+      </c>
+      <c r="BO39" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ce654b0e29e243c2a973d4f2da16328c.mp3</t>
+        </is>
+      </c>
+      <c r="BP39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 2 秒 </t>
+        </is>
+      </c>
+      <c r="BQ39" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:27:50</t>
+        </is>
+      </c>
+      <c r="BR39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT39" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV39" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW39" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ39" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>旅行社工作人员</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM40" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:21:56</t>
+        </is>
+      </c>
+      <c r="BN40" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:21:56</t>
+        </is>
+      </c>
+      <c r="BO40" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/621680565b774e0680af6c501e9b88f5.mp3</t>
+        </is>
+      </c>
+      <c r="BP40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 51 秒 </t>
+        </is>
+      </c>
+      <c r="BQ40" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:20:02</t>
+        </is>
+      </c>
+      <c r="BR40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT40" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV40" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW40" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ40" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE41" t="inlineStr">
+        <is>
+          <t>故事性</t>
+        </is>
+      </c>
+      <c r="BF41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM41" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:17:56</t>
+        </is>
+      </c>
+      <c r="BN41" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:17:56</t>
+        </is>
+      </c>
+      <c r="BO41" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/e4660a6e7b1b4fc7ae2a637e5cfa8292.mp3</t>
+        </is>
+      </c>
+      <c r="BP41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 </t>
+        </is>
+      </c>
+      <c r="BQ41" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:15:53</t>
+        </is>
+      </c>
+      <c r="BR41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT41" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV41" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW41" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ41" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>46-55岁</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>浙江省外</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>西南地区（渝、川、贵、云、藏）</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM42" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:10:53</t>
+        </is>
+      </c>
+      <c r="BN42" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:10:53</t>
+        </is>
+      </c>
+      <c r="BO42" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/bda17dbf386f421389ed6370f811d70d.mp3</t>
+        </is>
+      </c>
+      <c r="BP42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 4 秒 </t>
+        </is>
+      </c>
+      <c r="BQ42" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:07:46</t>
+        </is>
+      </c>
+      <c r="BR42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT42" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV42" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW42" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ42" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM43" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:00:43</t>
+        </is>
+      </c>
+      <c r="BN43" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:00:43</t>
+        </is>
+      </c>
+      <c r="BO43" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/86b9a3463f6b40988e95832b993002f4.mp3</t>
+        </is>
+      </c>
+      <c r="BP43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 26 秒 </t>
+        </is>
+      </c>
+      <c r="BQ43" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:58:14</t>
+        </is>
+      </c>
+      <c r="BR43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT43" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV43" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW43" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ43" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>人工讲解导览</t>
+        </is>
+      </c>
+      <c r="BE44" t="inlineStr">
+        <is>
+          <t>专业知识</t>
+        </is>
+      </c>
+      <c r="BF44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM44" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:57:25</t>
+        </is>
+      </c>
+      <c r="BN44" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:57:25</t>
+        </is>
+      </c>
+      <c r="BO44" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a20165306c164ddfa57672b5816d8b5c.mp3</t>
+        </is>
+      </c>
+      <c r="BP44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 12 秒 </t>
+        </is>
+      </c>
+      <c r="BQ44" t="inlineStr">
+        <is>
+          <t>2026-06-10 14:55:09</t>
+        </is>
+      </c>
+      <c r="BR44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT44" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV44" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW44" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ44" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2次及以上</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM45" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:40:49</t>
+        </is>
+      </c>
+      <c r="BN45" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:40:49</t>
+        </is>
+      </c>
+      <c r="BO45" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/53b5194f2d7c4bc0ba8dd14e9afe4caa.mp3</t>
+        </is>
+      </c>
+      <c r="BP45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 49 秒 </t>
+        </is>
+      </c>
+      <c r="BQ45" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:38:57</t>
+        </is>
+      </c>
+      <c r="BR45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT45" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV45" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体博览城</t>
+        </is>
+      </c>
+      <c r="BW45" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ45" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BF46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM46" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:36:31</t>
+        </is>
+      </c>
+      <c r="BN46" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:36:31</t>
+        </is>
+      </c>
+      <c r="BO46" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/d5ec9c3050de4f11b78de3480848d88f.mp3</t>
+        </is>
+      </c>
+      <c r="BP46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 23 秒 </t>
+        </is>
+      </c>
+      <c r="BQ46" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:35:05</t>
+        </is>
+      </c>
+      <c r="BR46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT46" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV46" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体中心国博壁球馆</t>
+        </is>
+      </c>
+      <c r="BW46" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ46" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2次及以上</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BF47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM47" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:33:55</t>
+        </is>
+      </c>
+      <c r="BN47" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:33:55</t>
+        </is>
+      </c>
+      <c r="BO47" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/384cba67e55b4a6ba45ed7d200dd5945.mp3</t>
+        </is>
+      </c>
+      <c r="BP47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 38 秒 </t>
+        </is>
+      </c>
+      <c r="BQ47" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:32:15</t>
+        </is>
+      </c>
+      <c r="BR47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT47" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV47" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW47" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ47" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>游客</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>浙江省内</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BM48" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:30:06</t>
+        </is>
+      </c>
+      <c r="BN48" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:30:06</t>
+        </is>
+      </c>
+      <c r="BO48" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/b5f5c6a9b4f14082913aafc79904c9cd.mp3</t>
+        </is>
+      </c>
+      <c r="BP48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 51 秒 </t>
+        </is>
+      </c>
+      <c r="BQ48" t="inlineStr">
+        <is>
+          <t>2026-06-05 12:28:12</t>
+        </is>
+      </c>
+      <c r="BR48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT48" t="inlineStr">
+        <is>
+          <t>0,285,290,329</t>
+        </is>
+      </c>
+      <c r="BU48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV48" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BW48" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BX48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BY48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ48" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>待提交审核</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>游客</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2次及以上</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>36-45岁</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>浙江省内</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>华东地区（沪、苏、浙、皖、赣、鲁）</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr">
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AU39" t="inlineStr">
+      <c r="AU49" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AV39" t="inlineStr">
+      <c r="AV49" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BC49" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BF39" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BG39" t="inlineStr">
+      <c r="BG49" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BH39" t="inlineStr">
+      <c r="BH49" t="inlineStr">
         <is>
           <t>会推荐</t>
         </is>
       </c>
-      <c r="BI39" t="inlineStr">
+      <c r="BI49" t="inlineStr">
         <is>
           <t>空中花园标识标牌太少</t>
         </is>
       </c>
-      <c r="BM39" t="inlineStr">
+      <c r="BM49" t="inlineStr">
         <is>
           <t>2026-06-05 12:22:25</t>
         </is>
       </c>
-      <c r="BN39" t="inlineStr">
+      <c r="BN49" t="inlineStr">
         <is>
           <t>2026-06-05 12:22:25</t>
         </is>
       </c>
-      <c r="BO39" t="inlineStr">
+      <c r="BO49" t="inlineStr">
         <is>
           <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/2297f6f26a6345d181964498cafb05f3.mp3</t>
         </is>
       </c>
-      <c r="BP39" t="inlineStr">
+      <c r="BP49" t="inlineStr">
         <is>
           <t xml:space="preserve">2 分 23 秒 </t>
         </is>
       </c>
-      <c r="BQ39" t="inlineStr">
+      <c r="BQ49" t="inlineStr">
         <is>
           <t>2026-06-05 12:19:59</t>
         </is>
       </c>
-      <c r="BR39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT39" t="inlineStr">
+      <c r="BR49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT49" t="inlineStr">
         <is>
           <t>0,285,290,329</t>
         </is>
       </c>
-      <c r="BU39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV39" t="inlineStr">
+      <c r="BU49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV49" t="inlineStr">
         <is>
           <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体中心国博壁球馆</t>
         </is>
       </c>
-      <c r="BW39" t="inlineStr">
+      <c r="BW49" t="inlineStr">
         <is>
           <t>杭博访问员2</t>
         </is>
       </c>
-      <c r="BX39" t="inlineStr">
+      <c r="BX49" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="BY39" t="inlineStr">
+      <c r="BY49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BZ39" t="inlineStr">
+      <c r="BZ49" t="inlineStr">
         <is>
           <t>一期</t>
         </is>
